--- a/data/trans_orig/P57_AF_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P57_AF_R-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo afectivo bajo (Duke) en 2007</t>
+          <t>Población con apoyo afectivo bajo (Duke) en 2007 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>197571</t>
+          <t>196758</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>223501</t>
+          <t>223742</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>72,59%</t>
+          <t>72,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>82,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>211544</t>
+          <t>212656</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>234458</t>
+          <t>234640</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>81,1%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>417399</t>
+          <t>417579</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>451513</t>
+          <t>452028</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>78,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>84,81%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>48672</t>
+          <t>48431</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>74602</t>
+          <t>75415</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26380</t>
+          <t>26198</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>49294</t>
+          <t>48182</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>81498</t>
+          <t>80983</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>115612</t>
+          <t>115432</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,66%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>270238</t>
+          <t>269548</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>314713</t>
+          <t>314333</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>55,12%</t>
+          <t>54,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>64,2%</t>
+          <t>64,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>296767</t>
+          <t>296294</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>338285</t>
+          <t>338291</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>58,89%</t>
+          <t>58,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>581143</t>
+          <t>578432</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>641580</t>
+          <t>639329</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>58,45%</t>
+          <t>58,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>64,53%</t>
+          <t>64,31%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>175526</t>
+          <t>175906</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>220001</t>
+          <t>220691</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>44,88%</t>
+          <t>45,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>165664</t>
+          <t>165658</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>207182</t>
+          <t>207655</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>41,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>352608</t>
+          <t>354859</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>413045</t>
+          <t>415756</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>41,55%</t>
+          <t>41,82%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>129663</t>
+          <t>130855</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>166977</t>
+          <t>167115</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
+          <t>41,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>52,37%</t>
+          <t>52,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>119761</t>
+          <t>119477</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>156411</t>
+          <t>156127</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,63%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>261496</t>
+          <t>262472</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>312216</t>
+          <t>312075</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>40,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,72%</t>
+          <t>47,7%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>151869</t>
+          <t>151731</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>189183</t>
+          <t>187991</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>47,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>59,33%</t>
+          <t>58,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>179001</t>
+          <t>179285</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>215651</t>
+          <t>215935</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>53,37%</t>
+          <t>53,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,29%</t>
+          <t>64,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>342042</t>
+          <t>342183</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>392762</t>
+          <t>391786</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>52,28%</t>
+          <t>52,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>60,03%</t>
+          <t>59,88%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>211891</t>
+          <t>211581</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>247962</t>
+          <t>248733</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>59,08%</t>
+          <t>58,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>69,13%</t>
+          <t>69,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>210381</t>
+          <t>210640</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>248002</t>
+          <t>245750</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>56,64%</t>
+          <t>56,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>66,76%</t>
+          <t>66,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>433393</t>
+          <t>432042</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>484013</t>
+          <t>482936</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>59,36%</t>
+          <t>59,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>66,29%</t>
+          <t>66,14%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>110709</t>
+          <t>109938</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>146780</t>
+          <t>147090</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>123454</t>
+          <t>125706</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>161075</t>
+          <t>160816</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>43,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>246114</t>
+          <t>247191</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>296734</t>
+          <t>298085</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>40,83%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>125007</t>
+          <t>125129</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>152682</t>
+          <t>152811</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>61,49%</t>
+          <t>61,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>75,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>138873</t>
+          <t>141186</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>164302</t>
+          <t>165513</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>79,5%</t>
+          <t>80,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>272500</t>
+          <t>272584</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>310477</t>
+          <t>310907</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>66,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>75,83%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>50626</t>
+          <t>50497</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>78301</t>
+          <t>78179</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>42371</t>
+          <t>41160</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>67800</t>
+          <t>65487</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>99504</t>
+          <t>99074</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>137481</t>
+          <t>137397</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,51%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>143014</t>
+          <t>143345</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>175376</t>
+          <t>175575</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>52,81%</t>
+          <t>52,93%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>64,76%</t>
+          <t>64,83%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>138590</t>
+          <t>137489</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>170434</t>
+          <t>171140</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>49,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>61,53%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>288306</t>
+          <t>290565</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>334983</t>
+          <t>337422</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>52,52%</t>
+          <t>52,93%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>61,02%</t>
+          <t>61,47%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>95435</t>
+          <t>95236</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>127797</t>
+          <t>127466</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>47,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>107710</t>
+          <t>107004</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>139554</t>
+          <t>140655</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>38,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>50,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>213972</t>
+          <t>211533</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>260649</t>
+          <t>258390</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>38,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>47,48%</t>
+          <t>47,07%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>241006</t>
+          <t>240206</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>289152</t>
+          <t>290199</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>47,18%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>204097</t>
+          <t>202784</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>252339</t>
+          <t>253355</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>39,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>461776</t>
+          <t>460647</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>530085</t>
+          <t>530059</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>325875</t>
+          <t>324828</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>374021</t>
+          <t>374821</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>52,99%</t>
+          <t>52,82%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>60,94%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>384900</t>
+          <t>383884</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>433142</t>
+          <t>434455</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>60,4%</t>
+          <t>60,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>67,97%</t>
+          <t>68,18%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>722181</t>
+          <t>722207</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>790490</t>
+          <t>791619</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>63,21%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>515843</t>
+          <t>513094</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>564750</t>
+          <t>563268</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>69,06%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>76,01%</t>
+          <t>75,82%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>598394</t>
+          <t>600735</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>644143</t>
+          <t>644332</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>76,37%</t>
+          <t>76,67%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>82,21%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1130088</t>
+          <t>1129976</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1198456</t>
+          <t>1197320</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>78,44%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>178201</t>
+          <t>179683</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>227108</t>
+          <t>229857</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>139368</t>
+          <t>139179</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>185117</t>
+          <t>182776</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>328006</t>
+          <t>329142</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>396374</t>
+          <t>396486</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1935520</t>
+          <t>1931499</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2047449</t>
+          <t>2040308</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>59,15%</t>
+          <t>59,03%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>62,57%</t>
+          <t>62,36%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2009712</t>
+          <t>2014386</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2120774</t>
+          <t>2124563</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>59,51%</t>
+          <t>59,65%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>62,8%</t>
+          <t>62,91%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3977174</t>
+          <t>3970701</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4128712</t>
+          <t>4129880</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>59,81%</t>
+          <t>59,72%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>62,11%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1224577</t>
+          <t>1231718</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1336506</t>
+          <t>1340527</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1256448</t>
+          <t>1252659</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1367510</t>
+          <t>1362836</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2520536</t>
+          <t>2519368</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2672074</t>
+          <t>2678547</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>40,28%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo afectivo bajo (Duke) en 2012</t>
+          <t>Población con apoyo afectivo bajo (Duke) en 2012 (tasa de respuesta: 99,34%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>171162</t>
+          <t>170635</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>203993</t>
+          <t>203100</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>59,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>70,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>197222</t>
+          <t>196586</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>227016</t>
+          <t>226155</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>70,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>81,56%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>378132</t>
+          <t>377017</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>424734</t>
+          <t>422485</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>66,98%</t>
+          <t>66,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>75,23%</t>
+          <t>74,83%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>82224</t>
+          <t>83117</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>115055</t>
+          <t>115582</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>40,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>51324</t>
+          <t>52185</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>81118</t>
+          <t>81754</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>139823</t>
+          <t>142072</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>186425</t>
+          <t>187540</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>33,22%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>231926</t>
+          <t>232531</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>279216</t>
+          <t>279412</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>46,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>55,34%</t>
+          <t>55,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>246436</t>
+          <t>246994</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>293174</t>
+          <t>294793</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>47,05%</t>
+          <t>47,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>56,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>491765</t>
+          <t>489685</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>555996</t>
+          <t>560199</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>47,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>54,07%</t>
+          <t>54,48%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>225294</t>
+          <t>225098</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>272584</t>
+          <t>271979</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>44,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>54,03%</t>
+          <t>53,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>230591</t>
+          <t>228972</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>277329</t>
+          <t>276771</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>43,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>52,95%</t>
+          <t>52,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>472280</t>
+          <t>468077</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>536511</t>
+          <t>538591</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>45,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>52,18%</t>
+          <t>52,38%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>171345</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>207074</t>
+          <t>207937</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>52,75%</t>
+          <t>52,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,9%</t>
+          <t>64,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>208643</t>
+          <t>209180</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>244917</t>
+          <t>242235</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>61,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,28%</t>
+          <t>71,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>389919</t>
+          <t>391202</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>441466</t>
+          <t>441301</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>58,82%</t>
+          <t>59,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>66,6%</t>
+          <t>66,57%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>116972</t>
+          <t>116109</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>153126</t>
+          <t>152701</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>47,25%</t>
+          <t>47,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>93924</t>
+          <t>96606</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>130198</t>
+          <t>129661</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>221421</t>
+          <t>221586</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>272968</t>
+          <t>271685</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>40,99%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>154124</t>
+          <t>152239</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>191882</t>
+          <t>194207</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>40,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>52,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>195068</t>
+          <t>196214</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>235346</t>
+          <t>234069</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>50,15%</t>
+          <t>50,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>60,51%</t>
+          <t>60,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>359212</t>
+          <t>360095</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>418130</t>
+          <t>415225</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,87%</t>
+          <t>54,49%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>181135</t>
+          <t>178810</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>218893</t>
+          <t>220778</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>47,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>58,68%</t>
+          <t>59,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>153605</t>
+          <t>154882</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>193883</t>
+          <t>192737</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>49,85%</t>
+          <t>49,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>343838</t>
+          <t>346743</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>402756</t>
+          <t>401873</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>45,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>52,86%</t>
+          <t>52,74%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>97694</t>
+          <t>98077</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>127331</t>
+          <t>127049</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>45,95%</t>
+          <t>46,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>59,89%</t>
+          <t>59,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>132367</t>
+          <t>132940</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>160659</t>
+          <t>160091</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>60,28%</t>
+          <t>60,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>72,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>240610</t>
+          <t>236965</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>282110</t>
+          <t>279015</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>54,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>65,27%</t>
+          <t>64,56%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>85287</t>
+          <t>85569</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>114924</t>
+          <t>114541</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>40,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>54,05%</t>
+          <t>53,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>58932</t>
+          <t>59500</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>87224</t>
+          <t>86651</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>39,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>150099</t>
+          <t>153194</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>191599</t>
+          <t>195244</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>45,17%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>145854</t>
+          <t>143832</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>177207</t>
+          <t>178032</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>52,7%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>65,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>170517</t>
+          <t>169792</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>204139</t>
+          <t>200492</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>61,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>322899</t>
+          <t>325294</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>370994</t>
+          <t>372086</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>58,73%</t>
+          <t>59,16%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>67,47%</t>
+          <t>67,67%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>95720</t>
+          <t>94895</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>127073</t>
+          <t>129095</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>46,56%</t>
+          <t>47,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>72763</t>
+          <t>76410</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>106385</t>
+          <t>107110</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>178835</t>
+          <t>177743</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>226930</t>
+          <t>224535</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>40,84%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>337930</t>
+          <t>337904</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>389351</t>
+          <t>389662</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>59,31%</t>
+          <t>59,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>388224</t>
+          <t>390850</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>441575</t>
+          <t>444698</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>56,85%</t>
+          <t>57,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>65,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>741835</t>
+          <t>744781</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>816680</t>
+          <t>815777</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>55,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>60,98%</t>
+          <t>60,91%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>267080</t>
+          <t>266769</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>318501</t>
+          <t>318527</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,7 +6242,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>40,64%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>241332</t>
+          <t>238209</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>294683</t>
+          <t>292057</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>42,77%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>522657</t>
+          <t>523560</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>597502</t>
+          <t>594556</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>39,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>44,39%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>644997</t>
+          <t>645840</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>686800</t>
+          <t>683643</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>660850</t>
+          <t>660048</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>707285</t>
+          <t>704033</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>80,23%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1320783</t>
+          <t>1320709</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1380699</t>
+          <t>1378253</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>82,61%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>86,21%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>89187</t>
+          <t>92344</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>130990</t>
+          <t>130147</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>115407</t>
+          <t>118659</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>161842</t>
+          <t>162644</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>217980</t>
+          <t>220426</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>277896</t>
+          <t>277970</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,39%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2047014</t>
+          <t>2049151</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2164819</t>
+          <t>2166148</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>60,1%</t>
+          <t>60,17%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>63,56%</t>
+          <t>63,6%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2303002</t>
+          <t>2300373</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2419673</t>
+          <t>2417984</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>65,13%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>68,46%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4389377</t>
+          <t>4388709</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4546755</t>
+          <t>4554484</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>63,27%</t>
+          <t>63,26%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>65,65%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1240934</t>
+          <t>1239605</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1358739</t>
+          <t>1356602</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>39,83%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1112315</t>
+          <t>1114004</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1228986</t>
+          <t>1231615</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2390986</t>
+          <t>2383257</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2548364</t>
+          <t>2549032</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>36,74%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo afectivo bajo (Duke) en 2016</t>
+          <t>Población con apoyo afectivo bajo (Duke) en 2016 (tasa de respuesta: 99,53%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>173749</t>
+          <t>175822</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>207762</t>
+          <t>210819</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>59,57%</t>
+          <t>60,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>72,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>190569</t>
+          <t>189733</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>220267</t>
+          <t>220144</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>67,03%</t>
+          <t>66,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>77,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>375982</t>
+          <t>374347</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>420641</t>
+          <t>421259</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>65,28%</t>
+          <t>64,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>73,03%</t>
+          <t>73,14%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>83915</t>
+          <t>80858</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>117928</t>
+          <t>115855</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>39,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>64023</t>
+          <t>64146</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>93721</t>
+          <t>94557</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>155326</t>
+          <t>154708</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>199985</t>
+          <t>201620</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>35,01%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>386170</t>
+          <t>384826</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>420219</t>
+          <t>421599</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>76,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>84,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>403129</t>
+          <t>403578</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>439021</t>
+          <t>440270</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>77,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>800885</t>
+          <t>800405</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>851778</t>
+          <t>850278</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>78,38%</t>
+          <t>78,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>83,22%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>80360</t>
+          <t>78980</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>114409</t>
+          <t>115753</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>82144</t>
+          <t>80895</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>118036</t>
+          <t>117587</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>169965</t>
+          <t>171465</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>220858</t>
+          <t>221338</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,66%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>214428</t>
+          <t>213989</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>244335</t>
+          <t>244559</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>67,72%</t>
+          <t>67,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>77,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>237899</t>
+          <t>240011</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>268172</t>
+          <t>271391</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>70,92%</t>
+          <t>71,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>462530</t>
+          <t>461617</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>505791</t>
+          <t>505723</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>70,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>77,55%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>72324</t>
+          <t>72100</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>102231</t>
+          <t>102670</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>67253</t>
+          <t>64034</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>97526</t>
+          <t>95414</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>146293</t>
+          <t>146361</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>189554</t>
+          <t>190467</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,21%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>114777</t>
+          <t>114303</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>153149</t>
+          <t>149947</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>40,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>131151</t>
+          <t>131559</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>171006</t>
+          <t>171919</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,26%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>254971</t>
+          <t>254732</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>308955</t>
+          <t>311782</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>41,28%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>215757</t>
+          <t>218959</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>254129</t>
+          <t>254603</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,49%</t>
+          <t>59,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,89%</t>
+          <t>69,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>215353</t>
+          <t>214440</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>255208</t>
+          <t>254800</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,74%</t>
+          <t>55,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>66,05%</t>
+          <t>65,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>446309</t>
+          <t>443482</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>500293</t>
+          <t>500532</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,09%</t>
+          <t>58,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>66,27%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>166832</t>
+          <t>166752</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>188260</t>
+          <t>187955</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>79,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>176533</t>
+          <t>176214</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>196788</t>
+          <t>197074</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>80,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>349722</t>
+          <t>347804</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>380303</t>
+          <t>379560</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>81,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>88,53%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21895</t>
+          <t>22200</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>43323</t>
+          <t>43403</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21799</t>
+          <t>21513</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>42054</t>
+          <t>42373</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>48439</t>
+          <t>49182</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>79020</t>
+          <t>80938</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,88%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>176303</t>
+          <t>176116</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>205337</t>
+          <t>204291</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>67,0%</t>
+          <t>66,93%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>77,64%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>195466</t>
+          <t>194986</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>224270</t>
+          <t>224127</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>71,57%</t>
+          <t>71,39%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>82,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>378620</t>
+          <t>380365</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>419586</t>
+          <t>419743</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>70,61%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>78,28%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>57786</t>
+          <t>58832</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>86820</t>
+          <t>87007</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>48845</t>
+          <t>48988</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>77649</t>
+          <t>78129</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>116652</t>
+          <t>116495</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>157618</t>
+          <t>155873</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,07%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>492539</t>
+          <t>492942</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>536752</t>
+          <t>538382</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>75,43%</t>
+          <t>75,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>82,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>499328</t>
+          <t>499243</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>545883</t>
+          <t>546650</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>73,19%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>80,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1006898</t>
+          <t>1008265</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1068420</t>
+          <t>1071460</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>75,42%</t>
+          <t>75,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>80,25%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>116237</t>
+          <t>114607</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>160450</t>
+          <t>160047</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>136225</t>
+          <t>135458</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>182780</t>
+          <t>182865</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>266677</t>
+          <t>263637</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>328199</t>
+          <t>326832</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,48%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>634913</t>
+          <t>632059</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>676066</t>
+          <t>675040</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>706177</t>
+          <t>704959</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>744407</t>
+          <t>744336</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>85,46%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1350579</t>
+          <t>1350539</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1408262</t>
+          <t>1408095</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9870,7 +9870,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>88,02%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>98870</t>
+          <t>99896</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>140023</t>
+          <t>142877</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>80447</t>
+          <t>80518</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>118677</t>
+          <t>119895</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>191528</t>
+          <t>191695</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>249211</t>
+          <t>249251</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,7 +9978,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2443440</t>
+          <t>2446255</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2549433</t>
+          <t>2549832</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>72,4%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>75,45%</t>
+          <t>75,46%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2628925</t>
+          <t>2632941</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2732085</t>
+          <t>2732581</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>74,67%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>77,5%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5110015</t>
+          <t>5108940</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5256477</t>
+          <t>5254090</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>73,99%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>76,09%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>829591</t>
+          <t>829192</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>935584</t>
+          <t>932769</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>793816</t>
+          <t>793320</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>896976</t>
+          <t>892960</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1648449</t>
+          <t>1650836</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1794911</t>
+          <t>1795986</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>26,01%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo afectivo bajo (Duke) en 2023</t>
+          <t>Población con apoyo afectivo bajo (Duke) en 2023 (tasa de respuesta: 98,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>118602</t>
+          <t>117647</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>160507</t>
+          <t>160851</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,18%</t>
+          <t>52,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>139011</t>
+          <t>136558</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>167222</t>
+          <t>165140</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>48,36%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>57,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>267777</t>
+          <t>264855</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>318288</t>
+          <t>319248</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,49%</t>
+          <t>53,65%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>147070</t>
+          <t>146726</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>188975</t>
+          <t>189930</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>47,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>61,44%</t>
+          <t>61,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>120233</t>
+          <t>122315</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>148444</t>
+          <t>150897</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>42,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>51,64%</t>
+          <t>52,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>276744</t>
+          <t>275784</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>327255</t>
+          <t>330177</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>55,49%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>257332</t>
+          <t>257004</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>314737</t>
+          <t>317112</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>49,64%</t>
+          <t>49,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>61,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>250666</t>
+          <t>251089</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>291021</t>
+          <t>293993</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>48,89%</t>
+          <t>48,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>56,77%</t>
+          <t>57,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>518263</t>
+          <t>523580</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>591866</t>
+          <t>595899</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>50,27%</t>
+          <t>50,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>57,8%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>203653</t>
+          <t>201278</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>261058</t>
+          <t>261386</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>50,36%</t>
+          <t>50,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>221642</t>
+          <t>218670</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>261997</t>
+          <t>261574</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>43,23%</t>
+          <t>42,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>51,11%</t>
+          <t>51,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>439186</t>
+          <t>435153</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>512789</t>
+          <t>507472</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>49,22%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>106091</t>
+          <t>102242</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>138428</t>
+          <t>137501</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>45,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>142849</t>
+          <t>141934</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>175393</t>
+          <t>172967</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>51,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>254689</t>
+          <t>255453</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>302050</t>
+          <t>299292</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>40,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,44%</t>
+          <t>47,01%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>165120</t>
+          <t>166047</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>197457</t>
+          <t>201306</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>54,4%</t>
+          <t>54,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>65,05%</t>
+          <t>66,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>157779</t>
+          <t>160205</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>190323</t>
+          <t>191238</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>48,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>57,12%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>334670</t>
+          <t>337428</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>382031</t>
+          <t>381267</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>52,56%</t>
+          <t>52,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>60,0%</t>
+          <t>59,88%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>59687</t>
+          <t>60518</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>95371</t>
+          <t>94214</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>68381</t>
+          <t>67799</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>141621</t>
+          <t>142699</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>132375</t>
+          <t>142469</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>223215</t>
+          <t>221313</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,32%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>214327</t>
+          <t>215484</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>250011</t>
+          <t>249180</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>69,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>80,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>330198</t>
+          <t>329120</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>403438</t>
+          <t>404020</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>69,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>558302</t>
+          <t>560204</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>649142</t>
+          <t>639048</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,44%</t>
+          <t>71,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>81,77%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>154671</t>
+          <t>154245</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>168588</t>
+          <t>169487</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>182721</t>
+          <t>182948</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>195293</t>
+          <t>195404</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>340833</t>
+          <t>341291</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>361049</t>
+          <t>360747</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>88,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,38%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9470</t>
+          <t>8571</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23387</t>
+          <t>23813</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12981</t>
+          <t>12870</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25553</t>
+          <t>25326</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>25283</t>
+          <t>25585</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>45499</t>
+          <t>45041</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,66%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>82714</t>
+          <t>84464</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>109675</t>
+          <t>110936</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>41,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>83024</t>
+          <t>83695</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>106449</t>
+          <t>106309</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>172429</t>
+          <t>173510</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>208047</t>
+          <t>209590</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>39,83%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>159440</t>
+          <t>158179</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>186401</t>
+          <t>184651</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>59,25%</t>
+          <t>58,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>68,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>150607</t>
+          <t>150747</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>174032</t>
+          <t>173361</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>58,59%</t>
+          <t>58,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>67,7%</t>
+          <t>67,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>318124</t>
+          <t>316581</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>353742</t>
+          <t>352661</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>60,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>67,23%</t>
+          <t>67,02%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>314826</t>
+          <t>312389</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>371968</t>
+          <t>373674</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>50,61%</t>
+          <t>50,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>60,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>428777</t>
+          <t>429371</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>704473</t>
+          <t>681422</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>769984</t>
+          <t>774545</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1090108</t>
+          <t>1117058</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>52,54%</t>
+          <t>52,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>76,22%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>250033</t>
+          <t>248327</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>307175</t>
+          <t>309612</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>39,92%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>49,39%</t>
+          <t>49,78%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>139152</t>
+          <t>162203</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>414848</t>
+          <t>414254</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>375518</t>
+          <t>348568</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>695642</t>
+          <t>691081</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>47,15%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>241057</t>
+          <t>258251</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>757173</t>
+          <t>758813</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>82,02%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>585756</t>
+          <t>585942</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>620648</t>
+          <t>619395</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>81,9%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>719579</t>
+          <t>645410</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1369057</t>
+          <t>1368088</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>43,86%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>83,39%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>167975</t>
+          <t>166335</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>684091</t>
+          <t>666897</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>72,09%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>94812</t>
+          <t>96065</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>129704</t>
+          <t>129518</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>271551</t>
+          <t>272520</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>921029</t>
+          <t>995198</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>56,14%</t>
+          <t>60,66%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1347645</t>
+          <t>1388323</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1940319</t>
+          <t>1943104</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>56,51%</t>
+          <t>56,59%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1982363</t>
+          <t>1978061</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2366368</t>
+          <t>2390665</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>54,5%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>65,87%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3491972</t>
+          <t>3491842</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4156024</t>
+          <t>4185170</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13536,7 +13536,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>58,84%</t>
+          <t>59,25%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1493217</t>
+          <t>1490432</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2085891</t>
+          <t>2045213</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>43,41%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>60,75%</t>
+          <t>59,57%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1263154</t>
+          <t>1238857</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1647159</t>
+          <t>1651461</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2907034</t>
+          <t>2877888</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3571086</t>
+          <t>3571216</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,7 +13644,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>40,75%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">

--- a/data/trans_orig/P57_AF_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P57_AF_R-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>196758</t>
+          <t>194313</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>223742</t>
+          <t>222757</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>72,29%</t>
+          <t>71,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>82,21%</t>
+          <t>81,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>212656</t>
+          <t>212804</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>234640</t>
+          <t>234193</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>81,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>417579</t>
+          <t>418519</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>452028</t>
+          <t>453092</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>78,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>85,01%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>48431</t>
+          <t>49416</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>75415</t>
+          <t>77860</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26198</t>
+          <t>26645</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>48182</t>
+          <t>48034</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>80983</t>
+          <t>79919</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>115432</t>
+          <t>114492</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,48%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>269548</t>
+          <t>271748</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>314333</t>
+          <t>315510</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>55,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>64,12%</t>
+          <t>64,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>296294</t>
+          <t>297486</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>338291</t>
+          <t>339692</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>59,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>67,13%</t>
+          <t>67,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>578432</t>
+          <t>579063</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>639329</t>
+          <t>641863</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>58,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>64,31%</t>
+          <t>64,56%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>175906</t>
+          <t>174729</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>220691</t>
+          <t>218491</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>44,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>165658</t>
+          <t>164257</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>207655</t>
+          <t>206463</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>354859</t>
+          <t>352325</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>415756</t>
+          <t>415125</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>41,76%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>130855</t>
+          <t>130405</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>167115</t>
+          <t>167672</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>52,41%</t>
+          <t>52,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>119477</t>
+          <t>121165</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>156127</t>
+          <t>156868</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>46,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>262472</t>
+          <t>260192</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>312075</t>
+          <t>309019</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,7%</t>
+          <t>47,23%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>151731</t>
+          <t>151174</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>187991</t>
+          <t>188441</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>47,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>59,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>179285</t>
+          <t>178544</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>215935</t>
+          <t>214247</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>53,45%</t>
+          <t>53,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,38%</t>
+          <t>63,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>342183</t>
+          <t>345239</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>391786</t>
+          <t>394066</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>52,3%</t>
+          <t>52,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>59,88%</t>
+          <t>60,23%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>211581</t>
+          <t>211620</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>248733</t>
+          <t>249254</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>59,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>69,35%</t>
+          <t>69,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>210640</t>
+          <t>209541</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>245750</t>
+          <t>246724</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>56,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>66,16%</t>
+          <t>66,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>432042</t>
+          <t>432683</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>482936</t>
+          <t>482488</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>59,17%</t>
+          <t>59,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>66,08%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>109938</t>
+          <t>109417</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>147090</t>
+          <t>147051</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>41,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>125706</t>
+          <t>124732</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>160816</t>
+          <t>161915</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>43,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>247191</t>
+          <t>247639</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>298085</t>
+          <t>297444</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>40,74%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>125129</t>
+          <t>126833</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>152811</t>
+          <t>152323</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>61,55%</t>
+          <t>62,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>74,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>141186</t>
+          <t>141180</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>165513</t>
+          <t>166623</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>80,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>272584</t>
+          <t>272110</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>310907</t>
+          <t>310175</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>66,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>75,66%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>50497</t>
+          <t>50985</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>78179</t>
+          <t>76475</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>41160</t>
+          <t>40050</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>65487</t>
+          <t>65493</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>99074</t>
+          <t>99806</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>137397</t>
+          <t>137871</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>33,63%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>143345</t>
+          <t>143440</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>175575</t>
+          <t>176268</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>52,93%</t>
+          <t>52,97%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>64,83%</t>
+          <t>65,09%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>137489</t>
+          <t>137665</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>171140</t>
+          <t>170024</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>49,43%</t>
+          <t>49,49%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>61,53%</t>
+          <t>61,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>290565</t>
+          <t>289772</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>337422</t>
+          <t>335161</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>52,93%</t>
+          <t>52,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>61,47%</t>
+          <t>61,05%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>95236</t>
+          <t>94543</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>127466</t>
+          <t>127371</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>34,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>47,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>107004</t>
+          <t>108120</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>140655</t>
+          <t>140479</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>38,87%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>50,57%</t>
+          <t>50,51%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>211533</t>
+          <t>213794</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>258390</t>
+          <t>259183</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>38,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>47,21%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>240206</t>
+          <t>239996</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>290199</t>
+          <t>288894</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>39,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>46,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>202784</t>
+          <t>204898</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>253355</t>
+          <t>254391</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>39,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>460647</t>
+          <t>458479</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>530059</t>
+          <t>531893</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>42,47%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>324828</t>
+          <t>326133</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>374821</t>
+          <t>375031</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>52,82%</t>
+          <t>53,03%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>60,98%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>383884</t>
+          <t>382848</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>434455</t>
+          <t>432341</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>60,24%</t>
+          <t>60,08%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>68,18%</t>
+          <t>67,85%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>722207</t>
+          <t>720373</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>791619</t>
+          <t>793787</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>57,67%</t>
+          <t>57,53%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>63,21%</t>
+          <t>63,39%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>513094</t>
+          <t>514749</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>563268</t>
+          <t>564137</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>69,06%</t>
+          <t>69,28%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>75,82%</t>
+          <t>75,93%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>600735</t>
+          <t>601646</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>644332</t>
+          <t>644216</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1129976</t>
+          <t>1135015</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1197320</t>
+          <t>1199348</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>74,03%</t>
+          <t>74,36%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>78,57%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>179683</t>
+          <t>178814</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>229857</t>
+          <t>228202</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>139179</t>
+          <t>139295</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>182776</t>
+          <t>181865</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>329142</t>
+          <t>327114</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>396486</t>
+          <t>391447</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>25,64%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1931499</t>
+          <t>1929022</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2040308</t>
+          <t>2039205</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>58,95%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>62,32%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2014386</t>
+          <t>2014582</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2124563</t>
+          <t>2123827</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>62,89%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3970701</t>
+          <t>3973465</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4129880</t>
+          <t>4136987</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>59,72%</t>
+          <t>59,76%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>62,11%</t>
+          <t>62,22%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1231718</t>
+          <t>1232821</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1340527</t>
+          <t>1343004</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>41,05%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1252659</t>
+          <t>1253395</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1362836</t>
+          <t>1362640</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2519368</t>
+          <t>2512261</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2678547</t>
+          <t>2675783</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>37,78%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>40,24%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>170635</t>
+          <t>171029</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>203100</t>
+          <t>205170</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>59,62%</t>
+          <t>59,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>70,96%</t>
+          <t>71,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>196586</t>
+          <t>195399</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>226155</t>
+          <t>227817</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>70,63%</t>
+          <t>70,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>377017</t>
+          <t>379315</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>422485</t>
+          <t>423738</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>67,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>75,06%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>83117</t>
+          <t>81047</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>115582</t>
+          <t>115188</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>52185</t>
+          <t>50523</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>81754</t>
+          <t>82941</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>142072</t>
+          <t>140819</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>187540</t>
+          <t>185242</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>32,81%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>232531</t>
+          <t>230142</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>279412</t>
+          <t>278838</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>46,09%</t>
+          <t>45,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>55,38%</t>
+          <t>55,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>246994</t>
+          <t>245178</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>294793</t>
+          <t>293317</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>47,16%</t>
+          <t>46,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>56,28%</t>
+          <t>56,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>489685</t>
+          <t>490819</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>560199</t>
+          <t>556733</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>54,48%</t>
+          <t>54,14%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>225098</t>
+          <t>225672</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>271979</t>
+          <t>274368</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>44,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>54,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>228972</t>
+          <t>230448</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>276771</t>
+          <t>278587</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>43,72%</t>
+          <t>44,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>52,84%</t>
+          <t>53,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>468077</t>
+          <t>471543</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>538591</t>
+          <t>537457</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>45,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>52,27%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>171345</t>
+          <t>172967</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>207937</t>
+          <t>208286</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>52,88%</t>
+          <t>53,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>64,17%</t>
+          <t>64,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>209180</t>
+          <t>207301</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>242235</t>
+          <t>242714</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>61,73%</t>
+          <t>61,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>71,49%</t>
+          <t>71,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>391202</t>
+          <t>392198</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>441301</t>
+          <t>440016</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>59,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>66,38%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>116109</t>
+          <t>115760</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>152701</t>
+          <t>151079</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>46,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>96606</t>
+          <t>96127</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>129661</t>
+          <t>131540</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>221586</t>
+          <t>222871</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>271685</t>
+          <t>270689</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>33,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,99%</t>
+          <t>40,83%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>152239</t>
+          <t>154014</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>194207</t>
+          <t>194787</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>40,81%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>52,06%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>196214</t>
+          <t>195447</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>234069</t>
+          <t>236683</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>50,45%</t>
+          <t>50,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>60,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>360095</t>
+          <t>358730</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>415225</t>
+          <t>415164</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,7 +5170,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>47,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>178810</t>
+          <t>178230</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>220778</t>
+          <t>219003</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>47,94%</t>
+          <t>47,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>59,19%</t>
+          <t>58,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>154882</t>
+          <t>152268</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>192737</t>
+          <t>193504</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>49,55%</t>
+          <t>49,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>346743</t>
+          <t>346804</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>401873</t>
+          <t>403238</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>52,74%</t>
+          <t>52,92%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>98077</t>
+          <t>96703</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>127049</t>
+          <t>125846</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>45,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>59,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>132940</t>
+          <t>133147</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>160091</t>
+          <t>159791</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>60,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>236965</t>
+          <t>238921</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>279015</t>
+          <t>281346</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>54,83%</t>
+          <t>55,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>64,56%</t>
+          <t>65,09%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>85569</t>
+          <t>86772</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>114541</t>
+          <t>115915</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>40,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>53,87%</t>
+          <t>54,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>59500</t>
+          <t>59800</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>86651</t>
+          <t>86444</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>39,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>153194</t>
+          <t>150863</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>195244</t>
+          <t>193288</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>34,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>44,72%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>143832</t>
+          <t>144232</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>178032</t>
+          <t>177546</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>52,7%</t>
+          <t>52,85%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>65,23%</t>
+          <t>65,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>169792</t>
+          <t>168312</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>200492</t>
+          <t>201252</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>60,78%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>72,68%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>325294</t>
+          <t>322694</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>372086</t>
+          <t>368985</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>58,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>67,67%</t>
+          <t>67,11%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>94895</t>
+          <t>95381</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>129095</t>
+          <t>128695</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>76410</t>
+          <t>75650</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>107110</t>
+          <t>108590</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>177743</t>
+          <t>180844</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>224535</t>
+          <t>227135</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>41,31%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>337904</t>
+          <t>337676</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>389662</t>
+          <t>390397</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>51,48%</t>
+          <t>51,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>59,36%</t>
+          <t>59,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>390850</t>
+          <t>388945</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>444698</t>
+          <t>440770</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>56,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>65,12%</t>
+          <t>64,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>744781</t>
+          <t>743671</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>815777</t>
+          <t>814839</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>55,61%</t>
+          <t>55,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>60,91%</t>
+          <t>60,84%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>266769</t>
+          <t>266034</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>318527</t>
+          <t>318755</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>40,53%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>48,52%</t>
+          <t>48,56%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>238209</t>
+          <t>242137</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>292057</t>
+          <t>293962</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>43,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>523560</t>
+          <t>524498</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>594556</t>
+          <t>595666</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>44,39%</t>
+          <t>44,47%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>645840</t>
+          <t>644866</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>683643</t>
+          <t>682804</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>83,1%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>660048</t>
+          <t>663261</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>704033</t>
+          <t>705488</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>80,62%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1320709</t>
+          <t>1321948</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1378253</t>
+          <t>1378986</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>82,61%</t>
+          <t>82,69%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>86,26%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>92344</t>
+          <t>93183</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>130147</t>
+          <t>131121</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>118659</t>
+          <t>117204</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>162644</t>
+          <t>159431</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>220426</t>
+          <t>219693</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>277970</t>
+          <t>276731</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,31%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2049151</t>
+          <t>2056241</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2166148</t>
+          <t>2169055</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>60,17%</t>
+          <t>60,38%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>63,6%</t>
+          <t>63,69%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2300373</t>
+          <t>2301178</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2417984</t>
+          <t>2417346</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>65,13%</t>
+          <t>65,15%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>68,44%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4388709</t>
+          <t>4383012</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4554484</t>
+          <t>4554313</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,7 +6885,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>63,18%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1239605</t>
+          <t>1236698</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1356602</t>
+          <t>1349512</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1114004</t>
+          <t>1114642</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1231615</t>
+          <t>1230810</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2383257</t>
+          <t>2383428</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2549032</t>
+          <t>2554729</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>36,82%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>175822</t>
+          <t>175813</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>210819</t>
+          <t>210382</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>72,28%</t>
+          <t>72,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>189733</t>
+          <t>190168</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>220144</t>
+          <t>221160</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>66,74%</t>
+          <t>66,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,44%</t>
+          <t>77,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>374347</t>
+          <t>375907</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>421259</t>
+          <t>421065</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>64,99%</t>
+          <t>65,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>73,14%</t>
+          <t>73,11%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>80858</t>
+          <t>81295</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>115855</t>
+          <t>115864</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>64146</t>
+          <t>63130</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>94557</t>
+          <t>94122</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>154708</t>
+          <t>154902</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>201620</t>
+          <t>200060</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>34,73%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>384826</t>
+          <t>385353</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>421599</t>
+          <t>420055</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>76,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>83,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>403578</t>
+          <t>405170</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>440270</t>
+          <t>441016</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>77,44%</t>
+          <t>77,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>84,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>800405</t>
+          <t>799082</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>850278</t>
+          <t>853220</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>83,51%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>78980</t>
+          <t>80524</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>115753</t>
+          <t>115226</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>80895</t>
+          <t>80149</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>117587</t>
+          <t>115995</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>171465</t>
+          <t>168523</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>221338</t>
+          <t>222661</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,79%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>213989</t>
+          <t>214297</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>244559</t>
+          <t>245062</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>67,58%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>77,23%</t>
+          <t>77,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>240011</t>
+          <t>239056</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>271391</t>
+          <t>270651</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>80,91%</t>
+          <t>80,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>461617</t>
+          <t>463898</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>505723</t>
+          <t>507081</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>70,79%</t>
+          <t>71,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>77,76%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>72100</t>
+          <t>71597</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>102670</t>
+          <t>102362</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>64034</t>
+          <t>64774</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>95414</t>
+          <t>96369</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>146361</t>
+          <t>145003</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>190467</t>
+          <t>188186</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>28,86%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>114303</t>
+          <t>113268</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>149947</t>
+          <t>151065</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>131559</t>
+          <t>131724</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>171919</t>
+          <t>172003</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>44,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>254732</t>
+          <t>256928</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>311782</t>
+          <t>311346</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>41,22%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>218959</t>
+          <t>217841</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>254603</t>
+          <t>255638</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>59,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>69,02%</t>
+          <t>69,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>214440</t>
+          <t>214356</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>254800</t>
+          <t>254635</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,5%</t>
+          <t>55,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,95%</t>
+          <t>65,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>443482</t>
+          <t>443918</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>500532</t>
+          <t>498336</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>58,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,27%</t>
+          <t>65,98%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>166752</t>
+          <t>166555</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>187955</t>
+          <t>187168</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>79,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>176214</t>
+          <t>178010</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>197074</t>
+          <t>197945</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>81,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>347804</t>
+          <t>350417</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>379560</t>
+          <t>379761</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>81,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,58%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22200</t>
+          <t>22987</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>43403</t>
+          <t>43600</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21513</t>
+          <t>20642</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>42373</t>
+          <t>40577</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>49182</t>
+          <t>48981</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>80938</t>
+          <t>78325</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,27%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>176116</t>
+          <t>177212</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>204291</t>
+          <t>204290</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,7 +9109,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>66,93%</t>
+          <t>67,35%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>194986</t>
+          <t>194088</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>224127</t>
+          <t>222446</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>71,39%</t>
+          <t>71,06%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>380365</t>
+          <t>378492</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>419743</t>
+          <t>419495</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>70,58%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>78,28%</t>
+          <t>78,23%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>58832</t>
+          <t>58833</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>87007</t>
+          <t>85911</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9227,7 +9227,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>48988</t>
+          <t>50669</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>78129</t>
+          <t>79027</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>116495</t>
+          <t>116743</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>155873</t>
+          <t>157746</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,42%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>492942</t>
+          <t>492860</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>538382</t>
+          <t>538090</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,82 +9452,82 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
+          <t>75,48%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>82,4%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>488</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>522531</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>500514</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>544647</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>76,61%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>73,38%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>79,85%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>943</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>1038151</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>1007834</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>1070924</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>77,76%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
           <t>75,49%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>82,45%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>488</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>522531</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>499243</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>546650</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>76,61%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>73,19%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>80,14%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>943</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>1038151</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>1008265</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>1071460</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>77,76%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>75,52%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>80,21%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>114607</t>
+          <t>114899</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>160047</t>
+          <t>160129</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,82 +9565,82 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
+          <t>24,52%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>159577</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>137461</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>181594</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>23,39%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>20,15%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>26,62%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>296946</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>264173</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>327263</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>22,24%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>19,79%</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
           <t>24,51%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>159577</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>135458</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>182865</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>23,39%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>19,86%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>26,81%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>272</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>296946</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>263637</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>326832</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>22,24%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>19,75%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>24,48%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>632059</t>
+          <t>633284</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>675040</t>
+          <t>674585</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>81,56%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>87,05%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>704959</t>
+          <t>706541</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>744336</t>
+          <t>745518</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1350539</t>
+          <t>1351294</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1408095</t>
+          <t>1408202</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,7 +9865,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>99896</t>
+          <t>100351</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>142877</t>
+          <t>141652</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>80518</t>
+          <t>79336</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>119895</t>
+          <t>118313</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>191695</t>
+          <t>191588</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>249251</t>
+          <t>248496</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9983,7 +9983,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,53%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2446255</t>
+          <t>2444893</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2549832</t>
+          <t>2550717</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>75,46%</t>
+          <t>75,49%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2632941</t>
+          <t>2627909</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2732581</t>
+          <t>2732923</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>74,67%</t>
+          <t>74,53%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5108940</t>
+          <t>5114418</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5254090</t>
+          <t>5252865</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>74,07%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>76,09%</t>
+          <t>76,07%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>829192</t>
+          <t>828307</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>932769</t>
+          <t>934131</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>793320</t>
+          <t>792978</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>892960</t>
+          <t>897992</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1650836</t>
+          <t>1652061</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1795986</t>
+          <t>1790508</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>25,93%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>140729</t>
+          <t>155968</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>117647</t>
+          <t>136198</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>160851</t>
+          <t>173396</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>45,75%</t>
+          <t>49,46%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>43,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,3%</t>
+          <t>54,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>151554</t>
+          <t>167779</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>136558</t>
+          <t>153043</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>165140</t>
+          <t>181584</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>52,72%</t>
+          <t>53,57%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>48,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,45%</t>
+          <t>57,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>292284</t>
+          <t>323747</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>264855</t>
+          <t>301032</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>319248</t>
+          <t>347465</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>49,12%</t>
+          <t>51,5%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>47,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>55,28%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>166848</t>
+          <t>159403</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>146726</t>
+          <t>141975</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>189930</t>
+          <t>179173</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>54,25%</t>
+          <t>50,54%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,7%</t>
+          <t>45,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>61,75%</t>
+          <t>56,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>135901</t>
+          <t>145442</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>122315</t>
+          <t>131637</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>150897</t>
+          <t>160178</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>42,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,49%</t>
+          <t>51,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>302748</t>
+          <t>304844</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>275784</t>
+          <t>281126</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>330177</t>
+          <t>327559</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>50,88%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>44,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>55,49%</t>
+          <t>52,11%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>307577</t>
+          <t>315371</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>307577</t>
+          <t>315371</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>307577</t>
+          <t>315371</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>287455</t>
+          <t>313221</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>287455</t>
+          <t>313221</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>287455</t>
+          <t>313221</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>595032</t>
+          <t>628591</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>595032</t>
+          <t>628591</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>595032</t>
+          <t>628591</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>287168</t>
+          <t>297078</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>257004</t>
+          <t>269319</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>317112</t>
+          <t>327555</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>55,4%</t>
+          <t>55,98%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>50,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>61,17%</t>
+          <t>61,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>270874</t>
+          <t>287272</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>251089</t>
+          <t>265988</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>293993</t>
+          <t>308613</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>52,84%</t>
+          <t>52,8%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>48,98%</t>
+          <t>48,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>56,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>558041</t>
+          <t>584350</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>523580</t>
+          <t>551894</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>595899</t>
+          <t>622579</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>54,12%</t>
+          <t>54,37%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>50,78%</t>
+          <t>51,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>57,8%</t>
+          <t>57,93%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>231222</t>
+          <t>233569</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>201278</t>
+          <t>203092</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>261386</t>
+          <t>261328</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>44,02%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>49,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>241789</t>
+          <t>256831</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>218670</t>
+          <t>235490</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>261574</t>
+          <t>278115</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>47,16%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>43,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>51,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>473011</t>
+          <t>490400</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>435153</t>
+          <t>452171</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>507472</t>
+          <t>522856</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>45,88%</t>
+          <t>45,63%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>42,2%</t>
+          <t>42,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>49,22%</t>
+          <t>48,65%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>512663</t>
+          <t>544103</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>512663</t>
+          <t>544103</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>512663</t>
+          <t>544103</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1031052</t>
+          <t>1074750</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1031052</t>
+          <t>1074750</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1031052</t>
+          <t>1074750</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>120920</t>
+          <t>122940</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>102242</t>
+          <t>106395</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>137501</t>
+          <t>140962</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>46,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>157746</t>
+          <t>163319</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>141934</t>
+          <t>148363</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>172967</t>
+          <t>180840</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>47,35%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>43,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>51,92%</t>
+          <t>53,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>278666</t>
+          <t>286259</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>255453</t>
+          <t>264573</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>299292</t>
+          <t>306888</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>44,45%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>47,65%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>182628</t>
+          <t>180893</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>166047</t>
+          <t>162871</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>201306</t>
+          <t>197438</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>60,16%</t>
+          <t>59,54%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>54,7%</t>
+          <t>53,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,32%</t>
+          <t>64,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>175426</t>
+          <t>176910</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>160205</t>
+          <t>159389</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>191238</t>
+          <t>191866</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>52,65%</t>
+          <t>52,0%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>48,08%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>56,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>358054</t>
+          <t>357803</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>337428</t>
+          <t>337174</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>381267</t>
+          <t>379489</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>56,23%</t>
+          <t>55,55%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>52,99%</t>
+          <t>52,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>59,88%</t>
+          <t>58,92%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>303548</t>
+          <t>303833</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>303548</t>
+          <t>303833</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>303548</t>
+          <t>303833</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>333172</t>
+          <t>340229</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>333172</t>
+          <t>340229</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>333172</t>
+          <t>340229</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>636720</t>
+          <t>644062</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>636720</t>
+          <t>644062</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>636720</t>
+          <t>644062</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>77007</t>
+          <t>93134</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>60518</t>
+          <t>73164</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>94214</t>
+          <t>114161</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>111465</t>
+          <t>126339</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>67799</t>
+          <t>110523</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>142699</t>
+          <t>145702</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>188472</t>
+          <t>219473</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>142469</t>
+          <t>193857</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>221313</t>
+          <t>246393</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>31,34%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>232691</t>
+          <t>275255</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>215484</t>
+          <t>254228</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>249180</t>
+          <t>295225</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>75,13%</t>
+          <t>74,72%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,58%</t>
+          <t>69,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>80,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>360354</t>
+          <t>291342</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>329120</t>
+          <t>271979</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>404020</t>
+          <t>307158</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>76,38%</t>
+          <t>69,75%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,76%</t>
+          <t>65,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>73,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>593045</t>
+          <t>566598</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>560204</t>
+          <t>539678</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>639048</t>
+          <t>592214</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>75,88%</t>
+          <t>72,08%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,68%</t>
+          <t>68,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>75,34%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>309698</t>
+          <t>368389</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>309698</t>
+          <t>368389</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>309698</t>
+          <t>368389</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>471819</t>
+          <t>417681</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>471819</t>
+          <t>417681</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>471819</t>
+          <t>417681</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>781517</t>
+          <t>786071</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>781517</t>
+          <t>786071</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>781517</t>
+          <t>786071</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>163084</t>
+          <t>186369</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>154245</t>
+          <t>177340</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>169487</t>
+          <t>193527</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>190022</t>
+          <t>207988</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>182948</t>
+          <t>200383</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>195404</t>
+          <t>213976</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>88,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>353106</t>
+          <t>394356</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>341291</t>
+          <t>382937</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>360747</t>
+          <t>404723</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,74%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>14974</t>
+          <t>18561</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8571</t>
+          <t>11403</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23813</t>
+          <t>27590</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>18252</t>
+          <t>18835</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12870</t>
+          <t>12847</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25326</t>
+          <t>26440</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>33226</t>
+          <t>37397</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>25585</t>
+          <t>27030</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>45041</t>
+          <t>48816</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,31%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178058</t>
+          <t>204930</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178058</t>
+          <t>204930</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178058</t>
+          <t>204930</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>386332</t>
+          <t>431753</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>386332</t>
+          <t>431753</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>386332</t>
+          <t>431753</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>96677</t>
+          <t>101591</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>84464</t>
+          <t>88635</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>110936</t>
+          <t>115735</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>41,22%</t>
+          <t>42,83%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>94368</t>
+          <t>100043</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>83695</t>
+          <t>88176</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>106309</t>
+          <t>112099</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>42,5%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>191045</t>
+          <t>201634</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>173510</t>
+          <t>183932</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>209590</t>
+          <t>221666</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>37,76%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>41,51%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>172438</t>
+          <t>168609</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>158179</t>
+          <t>154465</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>184651</t>
+          <t>181565</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>58,78%</t>
+          <t>57,17%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>68,61%</t>
+          <t>67,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>162688</t>
+          <t>163707</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>150747</t>
+          <t>151651</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>173361</t>
+          <t>175574</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>62,07%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>58,64%</t>
+          <t>57,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>67,44%</t>
+          <t>66,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>335126</t>
+          <t>332316</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>316581</t>
+          <t>312284</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>352661</t>
+          <t>350018</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>63,69%</t>
+          <t>62,24%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>60,17%</t>
+          <t>58,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>65,55%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269115</t>
+          <t>270200</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269115</t>
+          <t>270200</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269115</t>
+          <t>270200</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526171</t>
+          <t>533950</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526171</t>
+          <t>533950</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526171</t>
+          <t>533950</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>344416</t>
+          <t>394662</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>312389</t>
+          <t>359531</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>373674</t>
+          <t>423947</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>55,37%</t>
+          <t>55,11%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>50,22%</t>
+          <t>50,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>60,08%</t>
+          <t>59,2%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>536814</t>
+          <t>403084</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>429371</t>
+          <t>376208</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>681422</t>
+          <t>428673</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>63,63%</t>
+          <t>52,71%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>49,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>56,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>881231</t>
+          <t>797746</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>774545</t>
+          <t>757814</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1117058</t>
+          <t>839431</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>53,87%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>51,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>76,22%</t>
+          <t>56,69%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>277585</t>
+          <t>321465</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>248327</t>
+          <t>292180</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>309612</t>
+          <t>356596</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>44,63%</t>
+          <t>44,89%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>49,78%</t>
+          <t>49,8%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>306811</t>
+          <t>361632</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>162203</t>
+          <t>336043</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>414254</t>
+          <t>388508</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>47,29%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>50,8%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>584395</t>
+          <t>683097</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>348568</t>
+          <t>641412</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>691081</t>
+          <t>723029</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>46,13%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>43,31%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>48,83%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>622001</t>
+          <t>716127</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>622001</t>
+          <t>716127</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>622001</t>
+          <t>716127</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>843625</t>
+          <t>764716</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>843625</t>
+          <t>764716</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>843625</t>
+          <t>764716</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1465626</t>
+          <t>1480843</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1465626</t>
+          <t>1480843</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1465626</t>
+          <t>1480843</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>551773</t>
+          <t>645295</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>258251</t>
+          <t>619734</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>758813</t>
+          <t>668465</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>59,64%</t>
+          <t>81,26%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>82,02%</t>
+          <t>84,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>603947</t>
+          <t>696338</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>585942</t>
+          <t>676918</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>619395</t>
+          <t>714990</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>81,75%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1155720</t>
+          <t>1341632</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>645410</t>
+          <t>1309228</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1368088</t>
+          <t>1374950</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>84,76%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>373375</t>
+          <t>148852</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>166335</t>
+          <t>125682</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>666897</t>
+          <t>174413</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>40,36%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>72,09%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>111513</t>
+          <t>131697</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>96065</t>
+          <t>113045</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>129518</t>
+          <t>151117</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>484888</t>
+          <t>280550</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>272520</t>
+          <t>247232</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>995198</t>
+          <t>312954</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>60,66%</t>
+          <t>19,29%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>925148</t>
+          <t>794147</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>925148</t>
+          <t>794147</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>925148</t>
+          <t>794147</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>715460</t>
+          <t>828035</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>715460</t>
+          <t>828035</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>715460</t>
+          <t>828035</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1640608</t>
+          <t>1622182</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1640608</t>
+          <t>1622182</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1640608</t>
+          <t>1622182</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1781775</t>
+          <t>1997035</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1388323</t>
+          <t>1925935</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1943104</t>
+          <t>2061694</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>51,89%</t>
+          <t>57,0%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>54,97%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>56,59%</t>
+          <t>58,84%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2116789</t>
+          <t>2152162</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1978061</t>
+          <t>2093941</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2390665</t>
+          <t>2208051</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>58,19%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>56,62%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>65,87%</t>
+          <t>59,7%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>3898565</t>
+          <t>4149198</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3491842</t>
+          <t>4062573</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4185170</t>
+          <t>4237959</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>55,2%</t>
+          <t>57,61%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>56,41%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>59,25%</t>
+          <t>58,84%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1651761</t>
+          <t>1506608</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1490432</t>
+          <t>1441949</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2045213</t>
+          <t>1577708</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>41,16%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>59,57%</t>
+          <t>45,03%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1512733</t>
+          <t>1546398</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1238857</t>
+          <t>1490509</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1651461</t>
+          <t>1604619</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>41,81%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>43,38%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>3164493</t>
+          <t>3053005</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2877888</t>
+          <t>2964244</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3571216</t>
+          <t>3139630</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>41,16%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>43,59%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3433536</t>
+          <t>3503643</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3433536</t>
+          <t>3503643</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3433536</t>
+          <t>3503643</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3629522</t>
+          <t>3698560</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3629522</t>
+          <t>3698560</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3629522</t>
+          <t>3698560</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7063058</t>
+          <t>7202203</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7063058</t>
+          <t>7202203</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7063058</t>
+          <t>7202203</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
